--- a/data/gravel/Sonder Broken Road ST 2025.xlsx
+++ b/data/gravel/Sonder Broken Road ST 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03244B93-3594-E24B-93B9-CC5F4876747D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF3CC9F3-C7B1-174D-9CF8-091086F97F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3900" yWindow="2520" windowWidth="24900" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="106">
   <si>
     <t>brand</t>
   </si>
@@ -1632,8 +1632,8 @@
       <c r="A44" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>72</v>
+      <c r="B44" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">

--- a/data/gravel/Sonder Broken Road ST 2025.xlsx
+++ b/data/gravel/Sonder Broken Road ST 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF3CC9F3-C7B1-174D-9CF8-091086F97F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9564C63-A41D-574B-9176-0866BB792DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3900" yWindow="2520" windowWidth="24900" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="107">
   <si>
     <t>brand</t>
   </si>
@@ -351,6 +351,9 @@
   </si>
   <si>
     <t>suspension</t>
+  </si>
+  <si>
+    <t>https://us.alpkit.com/cdn/shop/files/broken-road-steel-GX-AXS-grey_0566f160-958d-45bb-9427-af74c1744c45.jpg?v=1717521923&amp;width=768</t>
   </si>
 </sst>
 </file>
@@ -801,6 +804,11 @@
         <v>94</v>
       </c>
     </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>

--- a/data/gravel/Sonder Broken Road ST 2025.xlsx
+++ b/data/gravel/Sonder Broken Road ST 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9564C63-A41D-574B-9176-0866BB792DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{880C5527-ED8C-3746-A2D5-18E5042AACB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3900" yWindow="2520" windowWidth="24900" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="110">
   <si>
     <t>brand</t>
   </si>
@@ -354,6 +354,15 @@
   </si>
   <si>
     <t>https://us.alpkit.com/cdn/shop/files/broken-road-steel-GX-AXS-grey_0566f160-958d-45bb-9427-af74c1744c45.jpg?v=1717521923&amp;width=768</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Sheffield, South Yorkshire, United Kingdom</t>
   </si>
 </sst>
 </file>
@@ -755,7 +764,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U72"/>
+  <dimension ref="A1:U73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1825,6 +1834,17 @@
       <c r="A72" s="1" t="s">
         <v>67</v>
       </c>
+      <c r="B72" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>109</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/gravel/Sonder Broken Road ST 2025.xlsx
+++ b/data/gravel/Sonder Broken Road ST 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{880C5527-ED8C-3746-A2D5-18E5042AACB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0BD07C1-3895-F641-8891-3E2D925DEE3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3900" yWindow="2520" windowWidth="24900" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="116">
   <si>
     <t>brand</t>
   </si>
@@ -363,6 +363,24 @@
   </si>
   <si>
     <t>Sheffield, South Yorkshire, United Kingdom</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -764,7 +782,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U73"/>
+  <dimension ref="A1:U79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1681,168 +1699,198 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>45</v>
+        <v>111</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B51" s="1">
-        <v>31.6</v>
+        <v>112</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B53" s="1">
-        <v>36</v>
+        <v>114</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>49</v>
+        <v>115</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
+      </c>
+      <c r="B57" s="1">
+        <v>31.6</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>97</v>
+        <v>48</v>
+      </c>
+      <c r="B59" s="1">
+        <v>36</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B63" s="1">
-        <v>2</v>
+        <v>52</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B64" s="1">
-        <v>1</v>
+        <v>53</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B69" s="1">
-        <v>1049</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B70" s="1">
-        <v>2049</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>107</v>
+        <v>61</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B75" s="1">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B76" s="1">
+        <v>2049</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B79" s="1" t="s">
         <v>109</v>
       </c>
     </row>

--- a/data/gravel/Sonder Broken Road ST 2025.xlsx
+++ b/data/gravel/Sonder Broken Road ST 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0BD07C1-3895-F641-8891-3E2D925DEE3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54510F10-CA36-0E4C-BB9A-76EB7944698B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3900" yWindow="2520" windowWidth="24900" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -254,12 +254,6 @@
     <t>yes</t>
   </si>
   <si>
-    <t>front_center</t>
-  </si>
-  <si>
-    <t>trail</t>
-  </si>
-  <si>
     <t>Small</t>
   </si>
   <si>
@@ -323,9 +317,6 @@
     <t>flat bar</t>
   </si>
   <si>
-    <t>20% sag</t>
-  </si>
-  <si>
     <t>internal</t>
   </si>
   <si>
@@ -381,6 +372,15 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>100mm fork sagged 20%</t>
   </si>
 </sst>
 </file>
@@ -796,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
@@ -804,7 +804,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.3">
@@ -828,12 +828,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.3">
@@ -841,7 +841,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
@@ -853,19 +853,19 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C8" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="F8" s="11" t="s">
         <v>76</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>78</v>
       </c>
       <c r="G8" s="6"/>
       <c r="H8" s="11"/>
@@ -888,7 +888,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C9" s="12">
         <v>410</v>
@@ -921,7 +921,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C10" s="12">
         <v>588.9</v>
@@ -954,7 +954,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C11" s="12">
         <v>105</v>
@@ -987,7 +987,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C12" s="12">
         <v>67</v>
@@ -1020,7 +1020,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C13" s="12">
         <v>485</v>
@@ -1034,8 +1034,8 @@
       <c r="F13" s="12">
         <v>485</v>
       </c>
-      <c r="G13" s="6" t="s">
-        <v>96</v>
+      <c r="G13" s="8" t="s">
+        <v>115</v>
       </c>
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
@@ -1055,7 +1055,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C14" s="12">
         <v>73</v>
@@ -1088,7 +1088,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C15" s="1">
         <f>VALUE(LEFT(G15,3))</f>
@@ -1107,16 +1107,16 @@
         <v>440</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K15" s="12"/>
       <c r="L15" s="12"/>
@@ -1133,7 +1133,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C16" s="12">
         <v>60</v>
@@ -1166,7 +1166,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C17" s="1">
         <v>45</v>
@@ -1181,7 +1181,7 @@
         <v>45</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H17" s="12"/>
       <c r="I17" s="12"/>
@@ -1202,7 +1202,7 @@
         <v>19</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C18" s="12">
         <v>1116.5999999999999</v>
@@ -1232,7 +1232,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C19" s="12">
         <v>735</v>
@@ -1265,7 +1265,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C20" s="12">
         <v>410</v>
@@ -1298,7 +1298,7 @@
         <v>16</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C21" s="12">
         <v>585</v>
@@ -1328,13 +1328,21 @@
     </row>
     <row r="22" spans="1:20" ht="22" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="B22" s="6"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
+      <c r="C22" s="7">
+        <v>100</v>
+      </c>
+      <c r="D22" s="7">
+        <v>100</v>
+      </c>
+      <c r="E22" s="7">
+        <v>100</v>
+      </c>
+      <c r="F22" s="7">
+        <v>100</v>
+      </c>
       <c r="G22" s="7"/>
       <c r="N22" s="4"/>
       <c r="O22" s="4"/>
@@ -1345,9 +1353,20 @@
     </row>
     <row r="23" spans="1:20" ht="22" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F23" s="5"/>
+        <v>114</v>
+      </c>
+      <c r="C23" s="1">
+        <v>20</v>
+      </c>
+      <c r="D23" s="1">
+        <v>20</v>
+      </c>
+      <c r="E23" s="1">
+        <v>20</v>
+      </c>
+      <c r="F23" s="1">
+        <v>20</v>
+      </c>
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
@@ -1606,7 +1625,7 @@
         <v>70</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -1614,7 +1633,7 @@
         <v>71</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -1622,7 +1641,7 @@
         <v>33</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
@@ -1699,32 +1718,32 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
@@ -1732,7 +1751,7 @@
         <v>44</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
@@ -1753,7 +1772,7 @@
         <v>47</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
@@ -1789,7 +1808,7 @@
         <v>53</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
@@ -1797,7 +1816,7 @@
         <v>54</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
@@ -1883,15 +1902,15 @@
         <v>67</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
